--- a/import-templates/MDI-To-EDRS-Template.xlsx
+++ b/import-templates/MDI-To-EDRS-Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mc142/Documents/workspace/mortality-reporting/mdi-import/import-templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B82711-D1B8-EA46-9AEC-6E67EA7D3288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B05B99E-67D1-8A41-83EC-D6D4D97F6CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="660" yWindow="660" windowWidth="34560" windowHeight="20560" xr2:uid="{7A50F290-1C75-487E-9806-F93553E4E7CC}"/>
+    <workbookView xWindow="2560" yWindow="2680" windowWidth="34560" windowHeight="20560" xr2:uid="{7A50F290-1C75-487E-9806-F93553E4E7CC}"/>
   </bookViews>
   <sheets>
     <sheet name="MDI RAVEN Input Schema" sheetId="4" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="186">
   <si>
     <t>Sections</t>
   </si>
@@ -682,6 +682,14 @@
   </si>
   <si>
     <t>Location of Injury: Country</t>
+  </si>
+  <si>
+    <t>Certifier ID</t>
+  </si>
+  <si>
+    <t>Identifier of the Certifier such as NPI, SS, ID.
+Format: &lt;type&gt;:&lt;value&gt;
+Ex: NPI:1234567890</t>
   </si>
 </sst>
 </file>
@@ -1714,7 +1722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54CD1DC7-E143-4CF5-BEA9-4DABBAFFC7B0}">
-  <dimension ref="A1:AU76"/>
+  <dimension ref="A1:AU77"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="21" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.33203125" style="50" customWidth="1"/>
@@ -2947,7 +2955,7 @@
       <c r="H72" s="46"/>
       <c r="I72" s="47"/>
     </row>
-    <row r="73" spans="1:47" s="48" customFormat="1" ht="42" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:47" s="48" customFormat="1" ht="28" x14ac:dyDescent="0.3">
       <c r="A73" s="61"/>
       <c r="B73" s="79" t="s">
         <v>118</v>
@@ -2988,13 +2996,13 @@
       <c r="H75" s="46"/>
       <c r="I75" s="47"/>
     </row>
-    <row r="76" spans="1:47" s="48" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:47" s="48" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A76" s="61"/>
       <c r="B76" s="78" t="s">
-        <v>122</v>
+        <v>184</v>
       </c>
       <c r="C76" s="102" t="s">
-        <v>123</v>
+        <v>185</v>
       </c>
       <c r="D76" s="89"/>
       <c r="E76" s="89"/>
@@ -3003,13 +3011,28 @@
       <c r="H76" s="89"/>
       <c r="I76" s="47"/>
     </row>
+    <row r="77" spans="1:47" s="48" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="61"/>
+      <c r="B77" s="78" t="s">
+        <v>122</v>
+      </c>
+      <c r="C77" s="102" t="s">
+        <v>123</v>
+      </c>
+      <c r="D77" s="89"/>
+      <c r="E77" s="89"/>
+      <c r="F77" s="89"/>
+      <c r="G77" s="89"/>
+      <c r="H77" s="89"/>
+      <c r="I77" s="47"/>
+    </row>
   </sheetData>
   <sheetProtection deleteColumns="0" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="13">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="12">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2560A1C6-3FEA-4452-84E2-D4BC7FEE35BC}">
           <x14:formula1>
             <xm:f>'Drop Down List Values'!$B$2:$B$5</xm:f>
@@ -3050,25 +3073,19 @@
           <x14:formula1>
             <xm:f>'Drop Down List Values'!$M$2:$M$4</xm:f>
           </x14:formula1>
-          <xm:sqref>H71 D71 D76:H76</xm:sqref>
+          <xm:sqref>H71 D71 D77:H77</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{77990685-A35A-4CD2-A1C0-E931CAE699E2}">
           <x14:formula1>
             <xm:f>'Drop Down List Values'!$L$2:$L$7</xm:f>
           </x14:formula1>
-          <xm:sqref>H41 D41</xm:sqref>
+          <xm:sqref>H41 D41 D51:H51</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E0C755F2-6856-4118-9F77-76F8475243FA}">
           <x14:formula1>
             <xm:f>'Drop Down List Values'!#REF!</xm:f>
           </x14:formula1>
           <xm:sqref>E71:G71 E41:G42 E54:G54</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4462E45F-28EE-7C43-87D7-6FE56EB1D45E}">
-          <x14:formula1>
-            <xm:f>'Drop Down List Values'!$L$2:$L$7</xm:f>
-          </x14:formula1>
-          <xm:sqref>D51:H51</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F5D3D991-D7DB-7E4A-BB40-76B56585838B}">
           <x14:formula1>
@@ -3401,6 +3418,29 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="b541edd5-2552-480e-ada6-0e2c8d317108">YVWEJ5DVYS2U-421999773-68</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="b541edd5-2552-480e-ada6-0e2c8d317108">
+      <Url>https://cdcpartners.sharepoint.com/sites/NCHS/nvssmodcop/_layouts/15/DocIdRedir.aspx?ID=YVWEJ5DVYS2U-421999773-68</Url>
+      <Description>YVWEJ5DVYS2U-421999773-68</Description>
+    </_dlc_DocIdUrl>
+    <ShareFileCreator xmlns="780ae317-08c5-4e10-af93-dd385a8384a9" xsi:nil="true"/>
+    <ShareFileCreated xmlns="780ae317-08c5-4e10-af93-dd385a8384a9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008D4902BA52C7D94A994657A564808B2B" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e4455a60d2ff5f5fcd8815d6d89b5b66">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b541edd5-2552-480e-ada6-0e2c8d317108" xmlns:ns3="780ae317-08c5-4e10-af93-dd385a8384a9" xmlns:ns4="3146657c-56f4-4c0a-bb9c-a675121ac670" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d1d01ecd782f081d5d944fa263943fc4" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="b541edd5-2552-480e-ada6-0e2c8d317108"/>
@@ -3599,29 +3639,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="b541edd5-2552-480e-ada6-0e2c8d317108">YVWEJ5DVYS2U-421999773-68</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="b541edd5-2552-480e-ada6-0e2c8d317108">
-      <Url>https://cdcpartners.sharepoint.com/sites/NCHS/nvssmodcop/_layouts/15/DocIdRedir.aspx?ID=YVWEJ5DVYS2U-421999773-68</Url>
-      <Description>YVWEJ5DVYS2U-421999773-68</Description>
-    </_dlc_DocIdUrl>
-    <ShareFileCreator xmlns="780ae317-08c5-4e10-af93-dd385a8384a9" xsi:nil="true"/>
-    <ShareFileCreated xmlns="780ae317-08c5-4e10-af93-dd385a8384a9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF0D7A6D-D78F-4048-9348-0B4289842B11}">
   <ds:schemaRefs>
@@ -3631,21 +3648,9 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0980278E-2A79-4F44-8623-FE545C304BE1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{448710E8-BE9E-4C9E-A40A-0AC1DAE48E99}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="b541edd5-2552-480e-ada6-0e2c8d317108"/>
-    <ds:schemaRef ds:uri="780ae317-08c5-4e10-af93-dd385a8384a9"/>
-    <ds:schemaRef ds:uri="3146657c-56f4-4c0a-bb9c-a675121ac670"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3669,9 +3674,21 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{448710E8-BE9E-4C9E-A40A-0AC1DAE48E99}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0980278E-2A79-4F44-8623-FE545C304BE1}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b541edd5-2552-480e-ada6-0e2c8d317108"/>
+    <ds:schemaRef ds:uri="780ae317-08c5-4e10-af93-dd385a8384a9"/>
+    <ds:schemaRef ds:uri="3146657c-56f4-4c0a-bb9c-a675121ac670"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/import-templates/MDI-To-EDRS-Template.xlsx
+++ b/import-templates/MDI-To-EDRS-Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mc142/Documents/workspace/mortality-reporting/mdi-import/import-templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B05B99E-67D1-8A41-83EC-D6D4D97F6CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE7023D2-86B6-B340-9238-3081F0EBF3AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2560" yWindow="2680" windowWidth="34560" windowHeight="20560" xr2:uid="{7A50F290-1C75-487E-9806-F93553E4E7CC}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34560" windowHeight="20560" xr2:uid="{7A50F290-1C75-487E-9806-F93553E4E7CC}"/>
   </bookViews>
   <sheets>
     <sheet name="MDI RAVEN Input Schema" sheetId="4" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="190">
   <si>
     <t>Sections</t>
   </si>
@@ -504,9 +504,6 @@
     <t>Is the Certifer a Physician, a pronouncer, or other?</t>
   </si>
   <si>
-    <t>Medical Examiner/Coroner</t>
-  </si>
-  <si>
     <t>Decedent Gender</t>
   </si>
   <si>
@@ -567,9 +564,6 @@
     <t>Pregnant at time of death</t>
   </si>
   <si>
-    <t>Pronouncing &amp; Certifying physician</t>
-  </si>
-  <si>
     <t>Black or African American</t>
   </si>
   <si>
@@ -600,9 +594,6 @@
     <t>Not pregnant, but pregnant within 42 days of death</t>
   </si>
   <si>
-    <t>Certifying Physician</t>
-  </si>
-  <si>
     <t>Native Hawaiian or Other Pacific Islander</t>
   </si>
   <si>
@@ -687,9 +678,31 @@
     <t>Certifier ID</t>
   </si>
   <si>
-    <t>Identifier of the Certifier such as NPI, SS, ID.
-Format: &lt;type&gt;:&lt;value&gt;
-Ex: NPI:1234567890</t>
+    <t>Certified Date</t>
+  </si>
+  <si>
+    <t>Date of Certification</t>
+  </si>
+  <si>
+    <t>Certifier ID System</t>
+  </si>
+  <si>
+    <t>Identifier System of the Certifier such as NPI, SS, ID.
+Ex: NPI</t>
+  </si>
+  <si>
+    <t>Identifier Value of the Certifier 
+Format is based on the ID system
+Ex: 1234567890</t>
+  </si>
+  <si>
+    <t>Death certification by medical examiner or coroner (procedure)</t>
+  </si>
+  <si>
+    <t>Death certification and verification by physician (procedure)</t>
+  </si>
+  <si>
+    <t>Death certification by physician (procedure)</t>
   </si>
 </sst>
 </file>
@@ -1722,7 +1735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54CD1DC7-E143-4CF5-BEA9-4DABBAFFC7B0}">
-  <dimension ref="A1:AU77"/>
+  <dimension ref="A1:AU79"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="21" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.33203125" style="50" customWidth="1"/>
@@ -1972,7 +1985,7 @@
     <row r="17" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="54"/>
       <c r="B17" s="70" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C17" s="93"/>
       <c r="D17" s="13"/>
@@ -1985,7 +1998,7 @@
     <row r="18" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="54"/>
       <c r="B18" s="70" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C18" s="93"/>
       <c r="D18" s="13"/>
@@ -2292,10 +2305,10 @@
     <row r="39" spans="1:9" s="30" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A39" s="57"/>
       <c r="B39" s="74" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C39" s="97" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D39" s="86"/>
       <c r="E39" s="28"/>
@@ -2307,7 +2320,7 @@
     <row r="40" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="57"/>
       <c r="B40" s="74" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C40" s="97"/>
       <c r="D40" s="86"/>
@@ -2320,7 +2333,7 @@
     <row r="41" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="57"/>
       <c r="B41" s="74" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C41" s="97"/>
       <c r="D41" s="86"/>
@@ -2333,7 +2346,7 @@
     <row r="42" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="57"/>
       <c r="B42" s="74" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C42" s="97"/>
       <c r="D42" s="86"/>
@@ -2346,7 +2359,7 @@
     <row r="43" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="57"/>
       <c r="B43" s="74" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C43" s="97"/>
       <c r="D43" s="86"/>
@@ -2359,7 +2372,7 @@
     <row r="44" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="57"/>
       <c r="B44" s="74" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C44" s="97"/>
       <c r="D44" s="124"/>
@@ -2372,10 +2385,10 @@
     <row r="45" spans="1:9" s="30" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A45" s="57"/>
       <c r="B45" s="75" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C45" s="97" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D45" s="124"/>
       <c r="E45" s="124"/>
@@ -2387,7 +2400,7 @@
     <row r="46" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="57"/>
       <c r="B46" s="75" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C46" s="97"/>
       <c r="D46" s="86"/>
@@ -2400,7 +2413,7 @@
     <row r="47" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="57"/>
       <c r="B47" s="75" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C47" s="97"/>
       <c r="D47" s="86"/>
@@ -2413,7 +2426,7 @@
     <row r="48" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="57"/>
       <c r="B48" s="75" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C48" s="97"/>
       <c r="D48" s="86"/>
@@ -2426,7 +2439,7 @@
     <row r="49" spans="1:47" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="57"/>
       <c r="B49" s="75" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C49" s="97"/>
       <c r="D49" s="86"/>
@@ -2439,7 +2452,7 @@
     <row r="50" spans="1:47" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="57"/>
       <c r="B50" s="75" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C50" s="97"/>
       <c r="D50" s="86"/>
@@ -2903,7 +2916,7 @@
     </row>
     <row r="69" spans="1:47" s="121" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="117" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B69" s="118"/>
       <c r="C69" s="119"/>
@@ -2996,7 +3009,7 @@
       <c r="H75" s="46"/>
       <c r="I75" s="47"/>
     </row>
-    <row r="76" spans="1:47" s="48" customFormat="1" ht="39" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:47" s="48" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A76" s="61"/>
       <c r="B76" s="78" t="s">
         <v>184</v>
@@ -3011,13 +3024,13 @@
       <c r="H76" s="89"/>
       <c r="I76" s="47"/>
     </row>
-    <row r="77" spans="1:47" s="48" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:47" s="48" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A77" s="61"/>
       <c r="B77" s="78" t="s">
-        <v>122</v>
+        <v>181</v>
       </c>
       <c r="C77" s="102" t="s">
-        <v>123</v>
+        <v>186</v>
       </c>
       <c r="D77" s="89"/>
       <c r="E77" s="89"/>
@@ -3026,13 +3039,43 @@
       <c r="H77" s="89"/>
       <c r="I77" s="47"/>
     </row>
+    <row r="78" spans="1:47" s="48" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="61"/>
+      <c r="B78" s="78" t="s">
+        <v>182</v>
+      </c>
+      <c r="C78" s="102" t="s">
+        <v>183</v>
+      </c>
+      <c r="D78" s="89"/>
+      <c r="E78" s="89"/>
+      <c r="F78" s="89"/>
+      <c r="G78" s="89"/>
+      <c r="H78" s="89"/>
+      <c r="I78" s="47"/>
+    </row>
+    <row r="79" spans="1:47" s="48" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="61"/>
+      <c r="B79" s="78" t="s">
+        <v>122</v>
+      </c>
+      <c r="C79" s="102" t="s">
+        <v>123</v>
+      </c>
+      <c r="D79" s="89"/>
+      <c r="E79" s="89"/>
+      <c r="F79" s="89"/>
+      <c r="G79" s="89"/>
+      <c r="H79" s="89"/>
+      <c r="I79" s="47"/>
+    </row>
   </sheetData>
   <sheetProtection deleteColumns="0" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="12">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="13">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2560A1C6-3FEA-4452-84E2-D4BC7FEE35BC}">
           <x14:formula1>
             <xm:f>'Drop Down List Values'!$B$2:$B$5</xm:f>
@@ -3073,7 +3116,7 @@
           <x14:formula1>
             <xm:f>'Drop Down List Values'!$M$2:$M$4</xm:f>
           </x14:formula1>
-          <xm:sqref>H71 D71 D77:H77</xm:sqref>
+          <xm:sqref>H71 D71</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{77990685-A35A-4CD2-A1C0-E931CAE699E2}">
           <x14:formula1>
@@ -3105,6 +3148,12 @@
           </x14:formula1>
           <xm:sqref>D56:H56</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A9A4B97D-E7E8-D743-9EC4-A75102260628}">
+          <x14:formula1>
+            <xm:f>'Drop Down List Values'!$M$2:$M$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>D79:H79</xm:sqref>
+        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
@@ -3139,34 +3188,34 @@
         <v>25</v>
       </c>
       <c r="C1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D1" t="s">
         <v>125</v>
-      </c>
-      <c r="D1" t="s">
-        <v>126</v>
       </c>
       <c r="E1" t="s">
         <v>63</v>
       </c>
       <c r="F1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G1" t="s">
         <v>75</v>
       </c>
       <c r="H1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I1" t="s">
         <v>82</v>
       </c>
       <c r="J1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K1" t="s">
         <v>129</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>130</v>
-      </c>
-      <c r="L1" t="s">
-        <v>131</v>
       </c>
       <c r="M1" t="s">
         <v>122</v>
@@ -3174,10 +3223,10 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" t="s">
         <v>132</v>
-      </c>
-      <c r="B2" t="s">
-        <v>133</v>
       </c>
       <c r="C2" t="s">
         <v>30</v>
@@ -3186,45 +3235,45 @@
         <v>30</v>
       </c>
       <c r="E2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F2" t="s">
         <v>134</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>135</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I2" t="s">
+        <v>134</v>
+      </c>
+      <c r="J2" t="s">
         <v>136</v>
-      </c>
-      <c r="H2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I2" t="s">
-        <v>135</v>
-      </c>
-      <c r="J2" t="s">
-        <v>137</v>
       </c>
       <c r="K2" t="s">
         <v>92</v>
       </c>
       <c r="L2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="M2" t="s">
-        <v>124</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B3" t="s">
         <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E3" t="s">
         <v>65</v>
@@ -3233,7 +3282,7 @@
         <v>74</v>
       </c>
       <c r="G3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H3" t="s">
         <v>74</v>
@@ -3242,74 +3291,74 @@
         <v>74</v>
       </c>
       <c r="J3" t="s">
+        <v>141</v>
+      </c>
+      <c r="K3" t="s">
         <v>142</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>143</v>
       </c>
-      <c r="L3" t="s">
-        <v>144</v>
-      </c>
       <c r="M3" t="s">
-        <v>145</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C4" t="s">
         <v>146</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
         <v>147</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
         <v>148</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G4" t="s">
         <v>149</v>
       </c>
-      <c r="E4" t="s">
+      <c r="H4" t="s">
+        <v>145</v>
+      </c>
+      <c r="I4" t="s">
         <v>150</v>
       </c>
-      <c r="F4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="J4" t="s">
         <v>151</v>
       </c>
-      <c r="H4" t="s">
-        <v>147</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="K4" t="s">
         <v>152</v>
       </c>
-      <c r="J4" t="s">
+      <c r="L4" t="s">
         <v>153</v>
       </c>
-      <c r="K4" t="s">
-        <v>154</v>
-      </c>
-      <c r="L4" t="s">
-        <v>155</v>
-      </c>
       <c r="M4" t="s">
-        <v>156</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F5" t="s">
         <v>81</v>
@@ -3318,13 +3367,16 @@
         <v>81</v>
       </c>
       <c r="I5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J5" t="s">
         <v>99</v>
       </c>
       <c r="L5" t="s">
-        <v>160</v>
+        <v>157</v>
+      </c>
+      <c r="M5" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
@@ -3332,30 +3384,30 @@
         <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E6" t="s">
+        <v>158</v>
+      </c>
+      <c r="I6" t="s">
+        <v>159</v>
+      </c>
+      <c r="J6" t="s">
+        <v>160</v>
+      </c>
+      <c r="L6" t="s">
         <v>161</v>
-      </c>
-      <c r="I6" t="s">
-        <v>162</v>
-      </c>
-      <c r="J6" t="s">
-        <v>163</v>
-      </c>
-      <c r="L6" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="J7" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="L7" t="s">
         <v>81</v>
@@ -3368,6 +3420,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -3417,30 +3478,7 @@
 </spe:Receivers>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="b541edd5-2552-480e-ada6-0e2c8d317108">YVWEJ5DVYS2U-421999773-68</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="b541edd5-2552-480e-ada6-0e2c8d317108">
-      <Url>https://cdcpartners.sharepoint.com/sites/NCHS/nvssmodcop/_layouts/15/DocIdRedir.aspx?ID=YVWEJ5DVYS2U-421999773-68</Url>
-      <Description>YVWEJ5DVYS2U-421999773-68</Description>
-    </_dlc_DocIdUrl>
-    <ShareFileCreator xmlns="780ae317-08c5-4e10-af93-dd385a8384a9" xsi:nil="true"/>
-    <ShareFileCreated xmlns="780ae317-08c5-4e10-af93-dd385a8384a9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008D4902BA52C7D94A994657A564808B2B" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e4455a60d2ff5f5fcd8815d6d89b5b66">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b541edd5-2552-480e-ada6-0e2c8d317108" xmlns:ns3="780ae317-08c5-4e10-af93-dd385a8384a9" xmlns:ns4="3146657c-56f4-4c0a-bb9c-a675121ac670" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d1d01ecd782f081d5d944fa263943fc4" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="b541edd5-2552-480e-ada6-0e2c8d317108"/>
@@ -3639,7 +3677,29 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="b541edd5-2552-480e-ada6-0e2c8d317108">YVWEJ5DVYS2U-421999773-68</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="b541edd5-2552-480e-ada6-0e2c8d317108">
+      <Url>https://cdcpartners.sharepoint.com/sites/NCHS/nvssmodcop/_layouts/15/DocIdRedir.aspx?ID=YVWEJ5DVYS2U-421999773-68</Url>
+      <Description>YVWEJ5DVYS2U-421999773-68</Description>
+    </_dlc_DocIdUrl>
+    <ShareFileCreator xmlns="780ae317-08c5-4e10-af93-dd385a8384a9" xsi:nil="true"/>
+    <ShareFileCreated xmlns="780ae317-08c5-4e10-af93-dd385a8384a9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{448710E8-BE9E-4C9E-A40A-0AC1DAE48E99}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF0D7A6D-D78F-4048-9348-0B4289842B11}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
@@ -3647,33 +3707,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{448710E8-BE9E-4C9E-A40A-0AC1DAE48E99}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69E3EF86-6C9E-4C22-A476-13DA012C68C5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="780ae317-08c5-4e10-af93-dd385a8384a9"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="3146657c-56f4-4c0a-bb9c-a675121ac670"/>
-    <ds:schemaRef ds:uri="b541edd5-2552-480e-ada6-0e2c8d317108"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0980278E-2A79-4F44-8623-FE545C304BE1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3691,4 +3725,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69E3EF86-6C9E-4C22-A476-13DA012C68C5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="780ae317-08c5-4e10-af93-dd385a8384a9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="3146657c-56f4-4c0a-bb9c-a675121ac670"/>
+    <ds:schemaRef ds:uri="b541edd5-2552-480e-ada6-0e2c8d317108"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/import-templates/MDI-To-EDRS-Template.xlsx
+++ b/import-templates/MDI-To-EDRS-Template.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mc142/Documents/workspace/mortality-reporting/mdi-import/import-templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE7023D2-86B6-B340-9238-3081F0EBF3AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D5248D6-039F-D746-B7FF-8F2E833F608B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34560" windowHeight="20560" xr2:uid="{7A50F290-1C75-487E-9806-F93553E4E7CC}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="20560" xr2:uid="{7A50F290-1C75-487E-9806-F93553E4E7CC}"/>
   </bookViews>
   <sheets>
-    <sheet name="MDI RAVEN Input Schema" sheetId="4" r:id="rId1"/>
+    <sheet name="MDI and EDRS" sheetId="4" r:id="rId1"/>
     <sheet name="Drop Down List Values" sheetId="5" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="192">
   <si>
     <t>Sections</t>
   </si>
@@ -53,9 +53,6 @@
   </si>
   <si>
     <t>End of Cases</t>
-  </si>
-  <si>
-    <t>This Excel File can be imported into RAVEN2.0; converting into FHIR and importing into RAVEN</t>
   </si>
   <si>
     <t>File Id</t>
@@ -703,6 +700,15 @@
   </si>
   <si>
     <t>Death certification by physician (procedure)</t>
+  </si>
+  <si>
+    <t>Usecase</t>
+  </si>
+  <si>
+    <t>MDI and EDRS FHIR Profile</t>
+  </si>
+  <si>
+    <t>This Excel File can be imported into RAVEN. Mapping data in this file to MDI and EDRS FHIR Profile</t>
   </si>
 </sst>
 </file>
@@ -1003,7 +1009,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -1402,6 +1408,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1776,26 +1785,32 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50" t="s">
+        <v>189</v>
+      </c>
+      <c r="B2" s="127" t="s">
+        <v>190</v>
+      </c>
       <c r="C2" s="69" t="s">
-        <v>9</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="105.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="50" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="109"/>
       <c r="C3" s="110" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="4" customFormat="1" ht="40" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A4" s="51" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="63"/>
       <c r="C4" s="90" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -1807,10 +1822,10 @@
     <row r="5" spans="1:9" s="6" customFormat="1" ht="31" x14ac:dyDescent="0.3">
       <c r="A5" s="52"/>
       <c r="B5" s="106" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="91" t="s">
         <v>14</v>
-      </c>
-      <c r="C5" s="91" t="s">
-        <v>15</v>
       </c>
       <c r="D5" s="49"/>
       <c r="E5" s="49"/>
@@ -1822,10 +1837,10 @@
     <row r="6" spans="1:9" s="6" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A6" s="52"/>
       <c r="B6" s="107" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="91" t="s">
         <v>16</v>
-      </c>
-      <c r="C6" s="91" t="s">
-        <v>17</v>
       </c>
       <c r="D6" s="49"/>
       <c r="E6" s="49"/>
@@ -1836,11 +1851,11 @@
     </row>
     <row r="7" spans="1:9" s="8" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A7" s="53" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" s="64"/>
       <c r="C7" s="92" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
@@ -1852,10 +1867,10 @@
     <row r="8" spans="1:9" s="11" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A8" s="54"/>
       <c r="B8" s="70" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="93" t="s">
         <v>20</v>
-      </c>
-      <c r="C8" s="93" t="s">
-        <v>21</v>
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="9"/>
@@ -1867,10 +1882,10 @@
     <row r="9" spans="1:9" s="11" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A9" s="54"/>
       <c r="B9" s="70" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="93" t="s">
         <v>22</v>
-      </c>
-      <c r="C9" s="93" t="s">
-        <v>23</v>
       </c>
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
@@ -1882,10 +1897,10 @@
     <row r="10" spans="1:9" s="11" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A10" s="54"/>
       <c r="B10" s="70" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="93" t="s">
         <v>25</v>
-      </c>
-      <c r="C10" s="93" t="s">
-        <v>26</v>
       </c>
       <c r="D10" s="126"/>
       <c r="E10" s="126"/>
@@ -1897,10 +1912,10 @@
     <row r="11" spans="1:9" s="11" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A11" s="54"/>
       <c r="B11" s="71" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="93" t="s">
         <v>28</v>
-      </c>
-      <c r="C11" s="93" t="s">
-        <v>29</v>
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
@@ -1912,10 +1927,10 @@
     <row r="12" spans="1:9" s="11" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A12" s="54"/>
       <c r="B12" s="70" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="93" t="s">
         <v>31</v>
-      </c>
-      <c r="C12" s="93" t="s">
-        <v>32</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="9"/>
@@ -1927,10 +1942,10 @@
     <row r="13" spans="1:9" s="11" customFormat="1" ht="65" x14ac:dyDescent="0.3">
       <c r="A13" s="54"/>
       <c r="B13" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="93" t="s">
         <v>33</v>
-      </c>
-      <c r="C13" s="93" t="s">
-        <v>34</v>
       </c>
       <c r="D13" s="13"/>
       <c r="E13" s="9"/>
@@ -1942,10 +1957,10 @@
     <row r="14" spans="1:9" s="11" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A14" s="54"/>
       <c r="B14" s="70" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="93" t="s">
         <v>35</v>
-      </c>
-      <c r="C14" s="93" t="s">
-        <v>36</v>
       </c>
       <c r="D14" s="80"/>
       <c r="E14" s="12"/>
@@ -1957,7 +1972,7 @@
     <row r="15" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="54"/>
       <c r="B15" s="70" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C15" s="93"/>
       <c r="D15" s="13"/>
@@ -1970,10 +1985,10 @@
     <row r="16" spans="1:9" s="11" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A16" s="54"/>
       <c r="B16" s="70" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="93" t="s">
         <v>38</v>
-      </c>
-      <c r="C16" s="93" t="s">
-        <v>39</v>
       </c>
       <c r="D16" s="122"/>
       <c r="E16" s="123"/>
@@ -1985,7 +2000,7 @@
     <row r="17" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="54"/>
       <c r="B17" s="70" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C17" s="93"/>
       <c r="D17" s="13"/>
@@ -1998,7 +2013,7 @@
     <row r="18" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="54"/>
       <c r="B18" s="70" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C18" s="93"/>
       <c r="D18" s="13"/>
@@ -2011,7 +2026,7 @@
     <row r="19" spans="1:9" s="11" customFormat="1" ht="28" x14ac:dyDescent="0.3">
       <c r="A19" s="54"/>
       <c r="B19" s="72" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C19" s="93"/>
       <c r="D19" s="13"/>
@@ -2024,7 +2039,7 @@
     <row r="20" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="54"/>
       <c r="B20" s="70" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C20" s="93"/>
       <c r="D20" s="13"/>
@@ -2037,7 +2052,7 @@
     <row r="21" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="54"/>
       <c r="B21" s="70" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C21" s="93"/>
       <c r="D21" s="13"/>
@@ -2049,11 +2064,11 @@
     </row>
     <row r="22" spans="1:9" s="15" customFormat="1" ht="91" x14ac:dyDescent="0.3">
       <c r="A22" s="103" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B22" s="65"/>
       <c r="C22" s="94" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
@@ -2065,10 +2080,10 @@
     <row r="23" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="55"/>
       <c r="B23" s="108" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="95" t="s">
         <v>45</v>
-      </c>
-      <c r="C23" s="95" t="s">
-        <v>46</v>
       </c>
       <c r="D23" s="112"/>
       <c r="E23" s="113"/>
@@ -2080,10 +2095,10 @@
     <row r="24" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="55"/>
       <c r="B24" s="108" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="95" t="s">
         <v>47</v>
-      </c>
-      <c r="C24" s="95" t="s">
-        <v>48</v>
       </c>
       <c r="D24" s="82"/>
       <c r="E24" s="19"/>
@@ -2095,10 +2110,10 @@
     <row r="25" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="55"/>
       <c r="B25" s="108" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="95" t="s">
         <v>49</v>
-      </c>
-      <c r="C25" s="95" t="s">
-        <v>50</v>
       </c>
       <c r="D25" s="83"/>
       <c r="E25" s="20"/>
@@ -2110,10 +2125,10 @@
     <row r="26" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="55"/>
       <c r="B26" s="108" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="95" t="s">
         <v>51</v>
-      </c>
-      <c r="C26" s="95" t="s">
-        <v>52</v>
       </c>
       <c r="D26" s="83"/>
       <c r="E26" s="20"/>
@@ -2125,10 +2140,10 @@
     <row r="27" spans="1:9" s="18" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A27" s="55"/>
       <c r="B27" s="108" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="95" t="s">
         <v>53</v>
-      </c>
-      <c r="C27" s="95" t="s">
-        <v>54</v>
       </c>
       <c r="D27" s="83"/>
       <c r="E27" s="20"/>
@@ -2140,10 +2155,10 @@
     <row r="28" spans="1:9" s="18" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A28" s="55"/>
       <c r="B28" s="108" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="95" t="s">
         <v>55</v>
-      </c>
-      <c r="C28" s="95" t="s">
-        <v>56</v>
       </c>
       <c r="D28" s="83"/>
       <c r="E28" s="20"/>
@@ -2155,10 +2170,10 @@
     <row r="29" spans="1:9" s="18" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A29" s="55"/>
       <c r="B29" s="108" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" s="95" t="s">
         <v>57</v>
-      </c>
-      <c r="C29" s="95" t="s">
-        <v>58</v>
       </c>
       <c r="D29" s="83"/>
       <c r="E29" s="20"/>
@@ -2170,10 +2185,10 @@
     <row r="30" spans="1:9" s="18" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A30" s="55"/>
       <c r="B30" s="108" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="95" t="s">
         <v>59</v>
-      </c>
-      <c r="C30" s="95" t="s">
-        <v>60</v>
       </c>
       <c r="D30" s="81"/>
       <c r="E30" s="16"/>
@@ -2185,10 +2200,10 @@
     <row r="31" spans="1:9" s="18" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A31" s="55"/>
       <c r="B31" s="108" t="s">
+        <v>60</v>
+      </c>
+      <c r="C31" s="95" t="s">
         <v>61</v>
-      </c>
-      <c r="C31" s="95" t="s">
-        <v>62</v>
       </c>
       <c r="D31" s="83"/>
       <c r="E31" s="20"/>
@@ -2200,10 +2215,10 @@
     <row r="32" spans="1:9" s="18" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A32" s="55"/>
       <c r="B32" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="95" t="s">
         <v>63</v>
-      </c>
-      <c r="C32" s="95" t="s">
-        <v>64</v>
       </c>
       <c r="D32" s="84"/>
       <c r="E32" s="84"/>
@@ -2215,10 +2230,10 @@
     <row r="33" spans="1:9" s="18" customFormat="1" ht="65" x14ac:dyDescent="0.3">
       <c r="A33" s="55"/>
       <c r="B33" s="73" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" s="95" t="s">
         <v>66</v>
-      </c>
-      <c r="C33" s="95" t="s">
-        <v>67</v>
       </c>
       <c r="D33" s="85"/>
       <c r="E33" s="22"/>
@@ -2230,10 +2245,10 @@
     <row r="34" spans="1:9" s="18" customFormat="1" ht="91" x14ac:dyDescent="0.3">
       <c r="A34" s="55"/>
       <c r="B34" s="73" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="95" t="s">
         <v>68</v>
-      </c>
-      <c r="C34" s="95" t="s">
-        <v>69</v>
       </c>
       <c r="D34" s="115"/>
       <c r="E34" s="23"/>
@@ -2245,10 +2260,10 @@
     <row r="35" spans="1:9" s="25" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="56"/>
       <c r="B35" s="73" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" s="95" t="s">
         <v>70</v>
-      </c>
-      <c r="C35" s="95" t="s">
-        <v>71</v>
       </c>
       <c r="D35" s="83"/>
       <c r="E35" s="20"/>
@@ -2260,10 +2275,10 @@
     <row r="36" spans="1:9" s="18" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A36" s="55"/>
       <c r="B36" s="73" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" s="95" t="s">
         <v>72</v>
-      </c>
-      <c r="C36" s="95" t="s">
-        <v>73</v>
       </c>
       <c r="D36" s="84"/>
       <c r="E36" s="84"/>
@@ -2275,10 +2290,10 @@
     <row r="37" spans="1:9" s="18" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A37" s="55"/>
       <c r="B37" s="73" t="s">
+        <v>74</v>
+      </c>
+      <c r="C37" s="95" t="s">
         <v>75</v>
-      </c>
-      <c r="C37" s="95" t="s">
-        <v>76</v>
       </c>
       <c r="D37" s="84"/>
       <c r="E37" s="84"/>
@@ -2289,11 +2304,11 @@
     </row>
     <row r="38" spans="1:9" s="27" customFormat="1" ht="91" x14ac:dyDescent="0.3">
       <c r="A38" s="104" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B38" s="66"/>
       <c r="C38" s="96" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D38" s="26"/>
       <c r="E38" s="26"/>
@@ -2305,10 +2320,10 @@
     <row r="39" spans="1:9" s="30" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A39" s="57"/>
       <c r="B39" s="74" t="s">
+        <v>166</v>
+      </c>
+      <c r="C39" s="97" t="s">
         <v>167</v>
-      </c>
-      <c r="C39" s="97" t="s">
-        <v>168</v>
       </c>
       <c r="D39" s="86"/>
       <c r="E39" s="28"/>
@@ -2320,7 +2335,7 @@
     <row r="40" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="57"/>
       <c r="B40" s="74" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C40" s="97"/>
       <c r="D40" s="86"/>
@@ -2333,7 +2348,7 @@
     <row r="41" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="57"/>
       <c r="B41" s="74" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C41" s="97"/>
       <c r="D41" s="86"/>
@@ -2346,7 +2361,7 @@
     <row r="42" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="57"/>
       <c r="B42" s="74" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C42" s="97"/>
       <c r="D42" s="86"/>
@@ -2359,7 +2374,7 @@
     <row r="43" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="57"/>
       <c r="B43" s="74" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C43" s="97"/>
       <c r="D43" s="86"/>
@@ -2372,7 +2387,7 @@
     <row r="44" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="57"/>
       <c r="B44" s="74" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C44" s="97"/>
       <c r="D44" s="124"/>
@@ -2385,10 +2400,10 @@
     <row r="45" spans="1:9" s="30" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A45" s="57"/>
       <c r="B45" s="75" t="s">
+        <v>173</v>
+      </c>
+      <c r="C45" s="97" t="s">
         <v>174</v>
-      </c>
-      <c r="C45" s="97" t="s">
-        <v>175</v>
       </c>
       <c r="D45" s="124"/>
       <c r="E45" s="124"/>
@@ -2400,7 +2415,7 @@
     <row r="46" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="57"/>
       <c r="B46" s="75" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C46" s="97"/>
       <c r="D46" s="86"/>
@@ -2413,7 +2428,7 @@
     <row r="47" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="57"/>
       <c r="B47" s="75" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C47" s="97"/>
       <c r="D47" s="86"/>
@@ -2426,7 +2441,7 @@
     <row r="48" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="57"/>
       <c r="B48" s="75" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C48" s="97"/>
       <c r="D48" s="86"/>
@@ -2439,7 +2454,7 @@
     <row r="49" spans="1:47" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="57"/>
       <c r="B49" s="75" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C49" s="97"/>
       <c r="D49" s="86"/>
@@ -2452,7 +2467,7 @@
     <row r="50" spans="1:47" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="57"/>
       <c r="B50" s="75" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C50" s="97"/>
       <c r="D50" s="86"/>
@@ -2465,10 +2480,10 @@
     <row r="51" spans="1:47" s="30" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A51" s="57"/>
       <c r="B51" s="74" t="s">
+        <v>78</v>
+      </c>
+      <c r="C51" s="97" t="s">
         <v>79</v>
-      </c>
-      <c r="C51" s="97" t="s">
-        <v>80</v>
       </c>
       <c r="D51" s="86"/>
       <c r="E51" s="86"/>
@@ -2480,10 +2495,10 @@
     <row r="52" spans="1:47" s="30" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A52" s="57"/>
       <c r="B52" s="105" t="s">
+        <v>81</v>
+      </c>
+      <c r="C52" s="97" t="s">
         <v>82</v>
-      </c>
-      <c r="C52" s="97" t="s">
-        <v>83</v>
       </c>
       <c r="D52" s="86"/>
       <c r="E52" s="86"/>
@@ -2494,11 +2509,11 @@
     </row>
     <row r="53" spans="1:47" s="33" customFormat="1" ht="65" x14ac:dyDescent="0.3">
       <c r="A53" s="111" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B53" s="67"/>
       <c r="C53" s="98" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D53" s="87"/>
       <c r="E53" s="31"/>
@@ -2510,10 +2525,10 @@
     <row r="54" spans="1:47" s="36" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A54" s="58"/>
       <c r="B54" s="76" t="s">
+        <v>85</v>
+      </c>
+      <c r="C54" s="99" t="s">
         <v>86</v>
-      </c>
-      <c r="C54" s="99" t="s">
-        <v>87</v>
       </c>
       <c r="D54" s="34"/>
       <c r="E54" s="34"/>
@@ -2525,10 +2540,10 @@
     <row r="55" spans="1:47" s="36" customFormat="1" ht="91" x14ac:dyDescent="0.3">
       <c r="A55" s="58"/>
       <c r="B55" s="76" t="s">
+        <v>87</v>
+      </c>
+      <c r="C55" s="99" t="s">
         <v>88</v>
-      </c>
-      <c r="C55" s="99" t="s">
-        <v>89</v>
       </c>
       <c r="D55" s="37"/>
       <c r="E55" s="37"/>
@@ -2540,10 +2555,10 @@
     <row r="56" spans="1:47" s="36" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A56" s="58"/>
       <c r="B56" s="76" t="s">
+        <v>89</v>
+      </c>
+      <c r="C56" s="99" t="s">
         <v>90</v>
-      </c>
-      <c r="C56" s="99" t="s">
-        <v>91</v>
       </c>
       <c r="D56" s="38"/>
       <c r="E56" s="38"/>
@@ -2555,10 +2570,10 @@
     <row r="57" spans="1:47" s="36" customFormat="1" ht="65" x14ac:dyDescent="0.3">
       <c r="A57" s="58"/>
       <c r="B57" s="76" t="s">
+        <v>92</v>
+      </c>
+      <c r="C57" s="99" t="s">
         <v>93</v>
-      </c>
-      <c r="C57" s="99" t="s">
-        <v>94</v>
       </c>
       <c r="D57" s="39"/>
       <c r="E57" s="39"/>
@@ -2570,10 +2585,10 @@
     <row r="58" spans="1:47" s="36" customFormat="1" ht="91" x14ac:dyDescent="0.3">
       <c r="A58" s="58"/>
       <c r="B58" s="76" t="s">
+        <v>94</v>
+      </c>
+      <c r="C58" s="99" t="s">
         <v>95</v>
-      </c>
-      <c r="C58" s="99" t="s">
-        <v>96</v>
       </c>
       <c r="D58" s="37"/>
       <c r="E58" s="37"/>
@@ -2585,10 +2600,10 @@
     <row r="59" spans="1:47" s="36" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A59" s="58"/>
       <c r="B59" s="76" t="s">
+        <v>96</v>
+      </c>
+      <c r="C59" s="99" t="s">
         <v>97</v>
-      </c>
-      <c r="C59" s="99" t="s">
-        <v>98</v>
       </c>
       <c r="D59" s="38"/>
       <c r="E59" s="38"/>
@@ -2599,11 +2614,11 @@
     </row>
     <row r="60" spans="1:47" s="41" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A60" s="59" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B60" s="68"/>
       <c r="C60" s="100" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D60" s="40"/>
       <c r="E60" s="40"/>
@@ -2615,10 +2630,10 @@
     <row r="61" spans="1:47" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="60"/>
       <c r="B61" s="77" t="s">
+        <v>101</v>
+      </c>
+      <c r="C61" s="101" t="s">
         <v>102</v>
-      </c>
-      <c r="C61" s="101" t="s">
-        <v>103</v>
       </c>
       <c r="D61" s="88"/>
       <c r="E61" s="42"/>
@@ -2630,10 +2645,10 @@
     <row r="62" spans="1:47" s="44" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A62" s="60"/>
       <c r="B62" s="77" t="s">
+        <v>103</v>
+      </c>
+      <c r="C62" s="101" t="s">
         <v>104</v>
-      </c>
-      <c r="C62" s="101" t="s">
-        <v>105</v>
       </c>
       <c r="D62" s="88"/>
       <c r="E62" s="42"/>
@@ -2645,10 +2660,10 @@
     <row r="63" spans="1:47" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="60"/>
       <c r="B63" s="77" t="s">
+        <v>105</v>
+      </c>
+      <c r="C63" s="101" t="s">
         <v>106</v>
-      </c>
-      <c r="C63" s="101" t="s">
-        <v>107</v>
       </c>
       <c r="D63" s="88"/>
       <c r="E63" s="88"/>
@@ -2660,10 +2675,10 @@
     <row r="64" spans="1:47" s="45" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A64" s="60"/>
       <c r="B64" s="77" t="s">
+        <v>107</v>
+      </c>
+      <c r="C64" s="101" t="s">
         <v>108</v>
-      </c>
-      <c r="C64" s="101" t="s">
-        <v>109</v>
       </c>
       <c r="D64" s="88"/>
       <c r="E64" s="88"/>
@@ -2713,7 +2728,7 @@
     <row r="65" spans="1:47" s="48" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="60"/>
       <c r="B65" s="77" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C65" s="101"/>
       <c r="D65" s="88"/>
@@ -2764,7 +2779,7 @@
     <row r="66" spans="1:47" s="48" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="60"/>
       <c r="B66" s="77" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C66" s="101"/>
       <c r="D66" s="88"/>
@@ -2815,7 +2830,7 @@
     <row r="67" spans="1:47" s="48" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="60"/>
       <c r="B67" s="77" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C67" s="101"/>
       <c r="D67" s="88"/>
@@ -2866,7 +2881,7 @@
     <row r="68" spans="1:47" s="48" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="60"/>
       <c r="B68" s="77" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C68" s="101"/>
       <c r="D68" s="88"/>
@@ -2916,7 +2931,7 @@
     </row>
     <row r="69" spans="1:47" s="121" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="117" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B69" s="118"/>
       <c r="C69" s="119"/>
@@ -2930,10 +2945,10 @@
     <row r="70" spans="1:47" s="48" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A70" s="61"/>
       <c r="B70" s="78" t="s">
+        <v>113</v>
+      </c>
+      <c r="C70" s="102" t="s">
         <v>114</v>
-      </c>
-      <c r="C70" s="102" t="s">
-        <v>115</v>
       </c>
       <c r="D70" s="89"/>
       <c r="E70" s="89"/>
@@ -2945,7 +2960,7 @@
     <row r="71" spans="1:47" s="48" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71" s="61"/>
       <c r="B71" s="78" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C71" s="102"/>
       <c r="D71" s="89"/>
@@ -2958,7 +2973,7 @@
     <row r="72" spans="1:47" s="48" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="61"/>
       <c r="B72" s="78" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C72" s="102"/>
       <c r="D72" s="89"/>
@@ -2971,7 +2986,7 @@
     <row r="73" spans="1:47" s="48" customFormat="1" ht="28" x14ac:dyDescent="0.3">
       <c r="A73" s="61"/>
       <c r="B73" s="79" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C73" s="102"/>
       <c r="D73" s="89"/>
@@ -2984,7 +2999,7 @@
     <row r="74" spans="1:47" s="48" customFormat="1" ht="28" x14ac:dyDescent="0.3">
       <c r="A74" s="61"/>
       <c r="B74" s="79" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C74" s="102"/>
       <c r="D74" s="89"/>
@@ -2997,10 +3012,10 @@
     <row r="75" spans="1:47" s="48" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A75" s="61"/>
       <c r="B75" s="78" t="s">
+        <v>119</v>
+      </c>
+      <c r="C75" s="102" t="s">
         <v>120</v>
-      </c>
-      <c r="C75" s="102" t="s">
-        <v>121</v>
       </c>
       <c r="D75" s="89"/>
       <c r="E75" s="46"/>
@@ -3012,10 +3027,10 @@
     <row r="76" spans="1:47" s="48" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A76" s="61"/>
       <c r="B76" s="78" t="s">
+        <v>183</v>
+      </c>
+      <c r="C76" s="102" t="s">
         <v>184</v>
-      </c>
-      <c r="C76" s="102" t="s">
-        <v>185</v>
       </c>
       <c r="D76" s="89"/>
       <c r="E76" s="89"/>
@@ -3027,10 +3042,10 @@
     <row r="77" spans="1:47" s="48" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A77" s="61"/>
       <c r="B77" s="78" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C77" s="102" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D77" s="89"/>
       <c r="E77" s="89"/>
@@ -3042,10 +3057,10 @@
     <row r="78" spans="1:47" s="48" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="61"/>
       <c r="B78" s="78" t="s">
+        <v>181</v>
+      </c>
+      <c r="C78" s="102" t="s">
         <v>182</v>
-      </c>
-      <c r="C78" s="102" t="s">
-        <v>183</v>
       </c>
       <c r="D78" s="89"/>
       <c r="E78" s="89"/>
@@ -3057,10 +3072,10 @@
     <row r="79" spans="1:47" s="48" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A79" s="61"/>
       <c r="B79" s="78" t="s">
+        <v>121</v>
+      </c>
+      <c r="C79" s="102" t="s">
         <v>122</v>
-      </c>
-      <c r="C79" s="102" t="s">
-        <v>123</v>
       </c>
       <c r="D79" s="89"/>
       <c r="E79" s="89"/>
@@ -3182,235 +3197,235 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1" t="s">
         <v>124</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" t="s">
         <v>125</v>
       </c>
-      <c r="E1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" t="s">
         <v>126</v>
       </c>
-      <c r="G1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J1" t="s">
         <v>127</v>
       </c>
-      <c r="I1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>128</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>129</v>
       </c>
-      <c r="L1" t="s">
-        <v>130</v>
-      </c>
       <c r="M1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B2" t="s">
         <v>131</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" t="s">
         <v>132</v>
       </c>
-      <c r="C2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>133</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>134</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
+        <v>133</v>
+      </c>
+      <c r="I2" t="s">
+        <v>133</v>
+      </c>
+      <c r="J2" t="s">
         <v>135</v>
       </c>
-      <c r="H2" t="s">
-        <v>134</v>
-      </c>
-      <c r="I2" t="s">
-        <v>134</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
+        <v>91</v>
+      </c>
+      <c r="L2" t="s">
         <v>136</v>
       </c>
-      <c r="K2" t="s">
-        <v>92</v>
-      </c>
-      <c r="L2" t="s">
-        <v>137</v>
-      </c>
       <c r="M2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
         <v>138</v>
       </c>
-      <c r="B3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" t="s">
         <v>139</v>
       </c>
-      <c r="D3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
+        <v>73</v>
+      </c>
+      <c r="I3" t="s">
+        <v>73</v>
+      </c>
+      <c r="J3" t="s">
         <v>140</v>
       </c>
-      <c r="H3" t="s">
-        <v>74</v>
-      </c>
-      <c r="I3" t="s">
-        <v>74</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>141</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>142</v>
       </c>
-      <c r="L3" t="s">
-        <v>143</v>
-      </c>
       <c r="M3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B4" t="s">
         <v>144</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>145</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>146</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>147</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G4" t="s">
         <v>148</v>
       </c>
-      <c r="F4" t="s">
-        <v>145</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I4" t="s">
         <v>149</v>
       </c>
-      <c r="H4" t="s">
-        <v>145</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>150</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>151</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>152</v>
       </c>
-      <c r="L4" t="s">
-        <v>153</v>
-      </c>
       <c r="M4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B5" t="s">
         <v>154</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E5" t="s">
         <v>155</v>
       </c>
-      <c r="C5" t="s">
+      <c r="F5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I5" t="s">
+        <v>144</v>
+      </c>
+      <c r="J5" t="s">
+        <v>98</v>
+      </c>
+      <c r="L5" t="s">
+        <v>156</v>
+      </c>
+      <c r="M5" t="s">
         <v>145</v>
-      </c>
-      <c r="D5" t="s">
-        <v>146</v>
-      </c>
-      <c r="E5" t="s">
-        <v>156</v>
-      </c>
-      <c r="F5" t="s">
-        <v>81</v>
-      </c>
-      <c r="H5" t="s">
-        <v>81</v>
-      </c>
-      <c r="I5" t="s">
-        <v>145</v>
-      </c>
-      <c r="J5" t="s">
-        <v>99</v>
-      </c>
-      <c r="L5" t="s">
-        <v>157</v>
-      </c>
-      <c r="M5" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E6" t="s">
+        <v>157</v>
+      </c>
+      <c r="I6" t="s">
         <v>158</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>159</v>
       </c>
-      <c r="J6" t="s">
+      <c r="L6" t="s">
         <v>160</v>
-      </c>
-      <c r="L6" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E7" t="s">
+        <v>161</v>
+      </c>
+      <c r="J7" t="s">
         <v>162</v>
       </c>
-      <c r="J7" t="s">
-        <v>163</v>
-      </c>
       <c r="L7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -3420,15 +3435,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -3478,7 +3484,7 @@
 </spe:Receivers>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008D4902BA52C7D94A994657A564808B2B" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e4455a60d2ff5f5fcd8815d6d89b5b66">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b541edd5-2552-480e-ada6-0e2c8d317108" xmlns:ns3="780ae317-08c5-4e10-af93-dd385a8384a9" xmlns:ns4="3146657c-56f4-4c0a-bb9c-a675121ac670" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d1d01ecd782f081d5d944fa263943fc4" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="b541edd5-2552-480e-ada6-0e2c8d317108"/>
@@ -3677,7 +3683,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_dlc_DocId xmlns="b541edd5-2552-480e-ada6-0e2c8d317108">YVWEJ5DVYS2U-421999773-68</_dlc_DocId>
@@ -3691,15 +3697,16 @@
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{448710E8-BE9E-4C9E-A40A-0AC1DAE48E99}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF0D7A6D-D78F-4048-9348-0B4289842B11}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
@@ -3707,7 +3714,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0980278E-2A79-4F44-8623-FE545C304BE1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3727,7 +3734,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69E3EF86-6C9E-4C22-A476-13DA012C68C5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
@@ -3743,4 +3750,12 @@
     <ds:schemaRef ds:uri="b541edd5-2552-480e-ada6-0e2c8d317108"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{448710E8-BE9E-4C9E-A40A-0AC1DAE48E99}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>